--- a/Output/万物有灵进化整理表.xlsx
+++ b/Output/万物有灵进化整理表.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -327,6 +327,8 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -766,7 +768,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>万物有灵进化整理表</t>
+          <t>万物有灵进化整理表（源码 4.9）</t>
         </is>
       </c>
     </row>
@@ -18146,7 +18148,7 @@
       <c r="H4" s="26" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n"/>
+      <c r="A5" s="44" t="n"/>
       <c r="B5" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18176,7 +18178,7 @@
       <c r="H5" s="29" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n"/>
+      <c r="A6" s="44" t="n"/>
       <c r="B6" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18210,7 +18212,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n"/>
+      <c r="A7" s="44" t="n"/>
       <c r="B7" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -18240,7 +18242,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n"/>
+      <c r="A8" s="45" t="n"/>
       <c r="B8" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -18300,7 +18302,7 @@
       <c r="H9" s="36" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n"/>
+      <c r="A10" s="44" t="n"/>
       <c r="B10" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18330,7 +18332,7 @@
       <c r="H10" s="31" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n"/>
+      <c r="A11" s="44" t="n"/>
       <c r="B11" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18360,7 +18362,7 @@
       <c r="H11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n"/>
+      <c r="A12" s="44" t="n"/>
       <c r="B12" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -18390,7 +18392,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n"/>
+      <c r="A13" s="44" t="n"/>
       <c r="B13" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -18420,7 +18422,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n"/>
+      <c r="A14" s="45" t="n"/>
       <c r="B14" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -18480,7 +18482,7 @@
       <c r="H15" s="36" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n"/>
+      <c r="A16" s="44" t="n"/>
       <c r="B16" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18510,7 +18512,7 @@
       <c r="H16" s="31" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n"/>
+      <c r="A17" s="44" t="n"/>
       <c r="B17" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18540,7 +18542,7 @@
       <c r="H17" s="29" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n"/>
+      <c r="A18" s="44" t="n"/>
       <c r="B18" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18570,7 +18572,7 @@
       <c r="H18" s="31" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n"/>
+      <c r="A19" s="44" t="n"/>
       <c r="B19" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -18600,7 +18602,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n"/>
+      <c r="A20" s="45" t="n"/>
       <c r="B20" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -18660,7 +18662,7 @@
       <c r="H21" s="36" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n"/>
+      <c r="A22" s="44" t="n"/>
       <c r="B22" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18690,7 +18692,7 @@
       <c r="H22" s="31" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="n"/>
+      <c r="A23" s="44" t="n"/>
       <c r="B23" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18720,7 +18722,7 @@
       <c r="H23" s="29" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n"/>
+      <c r="A24" s="44" t="n"/>
       <c r="B24" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -18750,7 +18752,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="n"/>
+      <c r="A25" s="44" t="n"/>
       <c r="B25" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -18780,7 +18782,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n"/>
+      <c r="A26" s="45" t="n"/>
       <c r="B26" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -18840,7 +18842,7 @@
       <c r="H27" s="36" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n"/>
+      <c r="A28" s="44" t="n"/>
       <c r="B28" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18874,7 +18876,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="n"/>
+      <c r="A29" s="44" t="n"/>
       <c r="B29" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -18908,7 +18910,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n"/>
+      <c r="A30" s="44" t="n"/>
       <c r="B30" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -18938,7 +18940,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="n"/>
+      <c r="A31" s="45" t="n"/>
       <c r="B31" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -18998,7 +19000,7 @@
       <c r="H32" s="26" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n"/>
+      <c r="A33" s="44" t="n"/>
       <c r="B33" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19028,7 +19030,7 @@
       <c r="H33" s="29" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n"/>
+      <c r="A34" s="44" t="n"/>
       <c r="B34" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19058,7 +19060,7 @@
       <c r="H34" s="31" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="n"/>
+      <c r="A35" s="44" t="n"/>
       <c r="B35" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19088,7 +19090,7 @@
       <c r="H35" s="29" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="n"/>
+      <c r="A36" s="44" t="n"/>
       <c r="B36" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19118,7 +19120,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n"/>
+      <c r="A37" s="45" t="n"/>
       <c r="B37" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -19178,7 +19180,7 @@
       <c r="H38" s="26" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="n"/>
+      <c r="A39" s="44" t="n"/>
       <c r="B39" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19208,7 +19210,7 @@
       <c r="H39" s="29" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="n"/>
+      <c r="A40" s="44" t="n"/>
       <c r="B40" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19238,7 +19240,7 @@
       <c r="H40" s="31" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="n"/>
+      <c r="A41" s="44" t="n"/>
       <c r="B41" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19268,7 +19270,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="n"/>
+      <c r="A42" s="45" t="n"/>
       <c r="B42" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -19328,7 +19330,7 @@
       <c r="H43" s="36" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="n"/>
+      <c r="A44" s="44" t="n"/>
       <c r="B44" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19362,7 +19364,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="n"/>
+      <c r="A45" s="44" t="n"/>
       <c r="B45" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19396,7 +19398,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="n"/>
+      <c r="A46" s="44" t="n"/>
       <c r="B46" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19426,7 +19428,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="n"/>
+      <c r="A47" s="45" t="n"/>
       <c r="B47" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -19486,7 +19488,7 @@
       <c r="H48" s="26" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="n"/>
+      <c r="A49" s="44" t="n"/>
       <c r="B49" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19520,7 +19522,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="n"/>
+      <c r="A50" s="44" t="n"/>
       <c r="B50" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19550,7 +19552,7 @@
       <c r="H50" s="31" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="n"/>
+      <c r="A51" s="44" t="n"/>
       <c r="B51" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19580,7 +19582,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="n"/>
+      <c r="A52" s="44" t="n"/>
       <c r="B52" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19610,7 +19612,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="n"/>
+      <c r="A53" s="44" t="n"/>
       <c r="B53" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -19640,7 +19642,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27" t="n"/>
+      <c r="A54" s="45" t="n"/>
       <c r="B54" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -19700,7 +19702,7 @@
       <c r="H55" s="36" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="27" t="n"/>
+      <c r="A56" s="44" t="n"/>
       <c r="B56" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19730,7 +19732,7 @@
       <c r="H56" s="31" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="n"/>
+      <c r="A57" s="44" t="n"/>
       <c r="B57" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19760,7 +19762,7 @@
       <c r="H57" s="29" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="27" t="n"/>
+      <c r="A58" s="44" t="n"/>
       <c r="B58" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19790,7 +19792,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="27" t="n"/>
+      <c r="A59" s="44" t="n"/>
       <c r="B59" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19820,7 +19822,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="27" t="n"/>
+      <c r="A60" s="45" t="n"/>
       <c r="B60" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -19880,7 +19882,7 @@
       <c r="H61" s="36" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="27" t="n"/>
+      <c r="A62" s="44" t="n"/>
       <c r="B62" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19914,7 +19916,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="27" t="n"/>
+      <c r="A63" s="44" t="n"/>
       <c r="B63" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -19948,7 +19950,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="27" t="n"/>
+      <c r="A64" s="44" t="n"/>
       <c r="B64" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -19978,7 +19980,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="n"/>
+      <c r="A65" s="45" t="n"/>
       <c r="B65" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20038,7 +20040,7 @@
       <c r="H66" s="26" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="27" t="n"/>
+      <c r="A67" s="44" t="n"/>
       <c r="B67" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20068,7 +20070,7 @@
       <c r="H67" s="29" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="27" t="n"/>
+      <c r="A68" s="44" t="n"/>
       <c r="B68" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20098,7 +20100,7 @@
       <c r="H68" s="31" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="27" t="n"/>
+      <c r="A69" s="44" t="n"/>
       <c r="B69" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20128,7 +20130,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="27" t="n"/>
+      <c r="A70" s="44" t="n"/>
       <c r="B70" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20158,7 +20160,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="27" t="n"/>
+      <c r="A71" s="44" t="n"/>
       <c r="B71" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20188,7 +20190,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="27" t="n"/>
+      <c r="A72" s="45" t="n"/>
       <c r="B72" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20248,7 +20250,7 @@
       <c r="H73" s="36" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="27" t="n"/>
+      <c r="A74" s="44" t="n"/>
       <c r="B74" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20278,7 +20280,7 @@
       <c r="H74" s="31" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="27" t="n"/>
+      <c r="A75" s="44" t="n"/>
       <c r="B75" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20308,7 +20310,7 @@
       <c r="H75" s="29" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="27" t="n"/>
+      <c r="A76" s="44" t="n"/>
       <c r="B76" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20338,7 +20340,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="27" t="n"/>
+      <c r="A77" s="45" t="n"/>
       <c r="B77" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20398,7 +20400,7 @@
       <c r="H78" s="26" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="27" t="n"/>
+      <c r="A79" s="44" t="n"/>
       <c r="B79" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20428,7 +20430,7 @@
       <c r="H79" s="29" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="27" t="n"/>
+      <c r="A80" s="44" t="n"/>
       <c r="B80" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20458,7 +20460,7 @@
       <c r="H80" s="31" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="27" t="n"/>
+      <c r="A81" s="44" t="n"/>
       <c r="B81" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20488,7 +20490,7 @@
       <c r="H81" s="29" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="27" t="n"/>
+      <c r="A82" s="44" t="n"/>
       <c r="B82" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20518,7 +20520,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="27" t="n"/>
+      <c r="A83" s="44" t="n"/>
       <c r="B83" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20548,7 +20550,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="27" t="n"/>
+      <c r="A84" s="44" t="n"/>
       <c r="B84" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20578,7 +20580,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="27" t="n"/>
+      <c r="A85" s="44" t="n"/>
       <c r="B85" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20608,7 +20610,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="27" t="n"/>
+      <c r="A86" s="44" t="n"/>
       <c r="B86" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20638,7 +20640,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="27" t="n"/>
+      <c r="A87" s="45" t="n"/>
       <c r="B87" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20698,7 +20700,7 @@
       <c r="H88" s="26" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="27" t="n"/>
+      <c r="A89" s="44" t="n"/>
       <c r="B89" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20728,7 +20730,7 @@
       <c r="H89" s="29" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="27" t="n"/>
+      <c r="A90" s="44" t="n"/>
       <c r="B90" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20762,7 +20764,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="27" t="n"/>
+      <c r="A91" s="44" t="n"/>
       <c r="B91" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20792,7 +20794,7 @@
       <c r="H91" s="29" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="27" t="n"/>
+      <c r="A92" s="44" t="n"/>
       <c r="B92" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20822,7 +20824,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27" t="n"/>
+      <c r="A93" s="44" t="n"/>
       <c r="B93" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20852,7 +20854,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="27" t="n"/>
+      <c r="A94" s="44" t="n"/>
       <c r="B94" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -20882,7 +20884,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27" t="n"/>
+      <c r="A95" s="45" t="n"/>
       <c r="B95" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -20942,7 +20944,7 @@
       <c r="H96" s="26" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="27" t="n"/>
+      <c r="A97" s="44" t="n"/>
       <c r="B97" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -20976,7 +20978,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="27" t="n"/>
+      <c r="A98" s="44" t="n"/>
       <c r="B98" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21010,7 +21012,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="27" t="n"/>
+      <c r="A99" s="44" t="n"/>
       <c r="B99" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21040,7 +21042,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="27" t="n"/>
+      <c r="A100" s="45" t="n"/>
       <c r="B100" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21100,7 +21102,7 @@
       <c r="H101" s="36" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="27" t="n"/>
+      <c r="A102" s="44" t="n"/>
       <c r="B102" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21130,7 +21132,7 @@
       <c r="H102" s="31" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="27" t="n"/>
+      <c r="A103" s="44" t="n"/>
       <c r="B103" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21160,7 +21162,7 @@
       <c r="H103" s="29" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="27" t="n"/>
+      <c r="A104" s="44" t="n"/>
       <c r="B104" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21190,7 +21192,7 @@
       <c r="H104" s="31" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="27" t="n"/>
+      <c r="A105" s="44" t="n"/>
       <c r="B105" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21220,7 +21222,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="27" t="n"/>
+      <c r="A106" s="44" t="n"/>
       <c r="B106" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21250,7 +21252,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="27" t="n"/>
+      <c r="A107" s="44" t="n"/>
       <c r="B107" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21280,7 +21282,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="27" t="n"/>
+      <c r="A108" s="44" t="n"/>
       <c r="B108" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21310,7 +21312,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="27" t="n"/>
+      <c r="A109" s="44" t="n"/>
       <c r="B109" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21340,7 +21342,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="27" t="n"/>
+      <c r="A110" s="45" t="n"/>
       <c r="B110" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21400,7 +21402,7 @@
       <c r="H111" s="36" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="27" t="n"/>
+      <c r="A112" s="44" t="n"/>
       <c r="B112" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21430,7 +21432,7 @@
       <c r="H112" s="31" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="27" t="n"/>
+      <c r="A113" s="44" t="n"/>
       <c r="B113" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21460,7 +21462,7 @@
       <c r="H113" s="29" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="27" t="n"/>
+      <c r="A114" s="44" t="n"/>
       <c r="B114" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21490,7 +21492,7 @@
       <c r="H114" s="31" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="27" t="n"/>
+      <c r="A115" s="44" t="n"/>
       <c r="B115" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21520,7 +21522,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="27" t="n"/>
+      <c r="A116" s="44" t="n"/>
       <c r="B116" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21550,7 +21552,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="27" t="n"/>
+      <c r="A117" s="44" t="n"/>
       <c r="B117" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21580,7 +21582,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="27" t="n"/>
+      <c r="A118" s="44" t="n"/>
       <c r="B118" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21610,7 +21612,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="27" t="n"/>
+      <c r="A119" s="44" t="n"/>
       <c r="B119" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21640,7 +21642,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="27" t="n"/>
+      <c r="A120" s="45" t="n"/>
       <c r="B120" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21700,7 +21702,7 @@
       <c r="H121" s="36" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="27" t="n"/>
+      <c r="A122" s="44" t="n"/>
       <c r="B122" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21730,7 +21732,7 @@
       <c r="H122" s="31" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="27" t="n"/>
+      <c r="A123" s="44" t="n"/>
       <c r="B123" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21760,7 +21762,7 @@
       <c r="H123" s="29" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="27" t="n"/>
+      <c r="A124" s="44" t="n"/>
       <c r="B124" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21790,7 +21792,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="27" t="n"/>
+      <c r="A125" s="45" t="n"/>
       <c r="B125" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -21850,7 +21852,7 @@
       <c r="H126" s="26" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="27" t="n"/>
+      <c r="A127" s="44" t="n"/>
       <c r="B127" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21880,7 +21882,7 @@
       <c r="H127" s="29" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="27" t="n"/>
+      <c r="A128" s="44" t="n"/>
       <c r="B128" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21910,7 +21912,7 @@
       <c r="H128" s="31" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="27" t="n"/>
+      <c r="A129" s="44" t="n"/>
       <c r="B129" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -21940,7 +21942,7 @@
       <c r="H129" s="29" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="27" t="n"/>
+      <c r="A130" s="44" t="n"/>
       <c r="B130" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -21970,7 +21972,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="27" t="n"/>
+      <c r="A131" s="44" t="n"/>
       <c r="B131" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -22000,7 +22002,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="27" t="n"/>
+      <c r="A132" s="44" t="n"/>
       <c r="B132" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -22030,7 +22032,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="27" t="n"/>
+      <c r="A133" s="44" t="n"/>
       <c r="B133" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22060,7 +22062,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="27" t="n"/>
+      <c r="A134" s="44" t="n"/>
       <c r="B134" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22090,7 +22092,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="27" t="n"/>
+      <c r="A135" s="45" t="n"/>
       <c r="B135" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22150,7 +22152,7 @@
       <c r="H136" s="26" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="27" t="n"/>
+      <c r="A137" s="44" t="n"/>
       <c r="B137" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22180,7 +22182,7 @@
       <c r="H137" s="29" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="27" t="n"/>
+      <c r="A138" s="44" t="n"/>
       <c r="B138" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22210,7 +22212,7 @@
       <c r="H138" s="31" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="27" t="n"/>
+      <c r="A139" s="44" t="n"/>
       <c r="B139" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -22240,7 +22242,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="27" t="n"/>
+      <c r="A140" s="45" t="n"/>
       <c r="B140" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22300,7 +22302,7 @@
       <c r="H141" s="36" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="27" t="n"/>
+      <c r="A142" s="44" t="n"/>
       <c r="B142" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22334,7 +22336,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="27" t="n"/>
+      <c r="A143" s="44" t="n"/>
       <c r="B143" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22368,7 +22370,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="27" t="n"/>
+      <c r="A144" s="44" t="n"/>
       <c r="B144" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -22398,7 +22400,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="27" t="n"/>
+      <c r="A145" s="45" t="n"/>
       <c r="B145" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22458,7 +22460,7 @@
       <c r="H146" s="26" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="27" t="n"/>
+      <c r="A147" s="44" t="n"/>
       <c r="B147" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22488,7 +22490,7 @@
       <c r="H147" s="29" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="27" t="n"/>
+      <c r="A148" s="44" t="n"/>
       <c r="B148" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22518,7 +22520,7 @@
       <c r="H148" s="31" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="27" t="n"/>
+      <c r="A149" s="44" t="n"/>
       <c r="B149" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22548,7 +22550,7 @@
       <c r="H149" s="29" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="27" t="n"/>
+      <c r="A150" s="44" t="n"/>
       <c r="B150" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -22578,7 +22580,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="27" t="n"/>
+      <c r="A151" s="45" t="n"/>
       <c r="B151" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22638,7 +22640,7 @@
       <c r="H152" s="26" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="27" t="n"/>
+      <c r="A153" s="44" t="n"/>
       <c r="B153" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22672,7 +22674,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="27" t="n"/>
+      <c r="A154" s="44" t="n"/>
       <c r="B154" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22702,7 +22704,7 @@
       <c r="H154" s="31" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="27" t="n"/>
+      <c r="A155" s="44" t="n"/>
       <c r="B155" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -22732,7 +22734,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="27" t="n"/>
+      <c r="A156" s="45" t="n"/>
       <c r="B156" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22792,7 +22794,7 @@
       <c r="H157" s="36" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="27" t="n"/>
+      <c r="A158" s="44" t="n"/>
       <c r="B158" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22826,7 +22828,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="27" t="n"/>
+      <c r="A159" s="44" t="n"/>
       <c r="B159" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22860,7 +22862,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="27" t="n"/>
+      <c r="A160" s="44" t="n"/>
       <c r="B160" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -22890,7 +22892,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="27" t="n"/>
+      <c r="A161" s="45" t="n"/>
       <c r="B161" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -22950,7 +22952,7 @@
       <c r="H162" s="26" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="27" t="n"/>
+      <c r="A163" s="44" t="n"/>
       <c r="B163" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -22984,7 +22986,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="27" t="n"/>
+      <c r="A164" s="44" t="n"/>
       <c r="B164" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23018,7 +23020,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="27" t="n"/>
+      <c r="A165" s="44" t="n"/>
       <c r="B165" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23048,7 +23050,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="27" t="n"/>
+      <c r="A166" s="45" t="n"/>
       <c r="B166" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23108,7 +23110,7 @@
       <c r="H167" s="36" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="27" t="n"/>
+      <c r="A168" s="44" t="n"/>
       <c r="B168" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23138,7 +23140,7 @@
       <c r="H168" s="31" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="27" t="n"/>
+      <c r="A169" s="44" t="n"/>
       <c r="B169" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23172,7 +23174,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="27" t="n"/>
+      <c r="A170" s="44" t="n"/>
       <c r="B170" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23202,7 +23204,7 @@
       <c r="H170" s="31" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="27" t="n"/>
+      <c r="A171" s="44" t="n"/>
       <c r="B171" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23232,7 +23234,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="27" t="n"/>
+      <c r="A172" s="44" t="n"/>
       <c r="B172" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23262,7 +23264,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="27" t="n"/>
+      <c r="A173" s="44" t="n"/>
       <c r="B173" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23292,7 +23294,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="27" t="n"/>
+      <c r="A174" s="44" t="n"/>
       <c r="B174" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23322,7 +23324,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="27" t="n"/>
+      <c r="A175" s="44" t="n"/>
       <c r="B175" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23352,7 +23354,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="27" t="n"/>
+      <c r="A176" s="45" t="n"/>
       <c r="B176" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23412,7 +23414,7 @@
       <c r="H177" s="36" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="27" t="n"/>
+      <c r="A178" s="44" t="n"/>
       <c r="B178" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23442,7 +23444,7 @@
       <c r="H178" s="31" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="27" t="n"/>
+      <c r="A179" s="44" t="n"/>
       <c r="B179" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23472,7 +23474,7 @@
       <c r="H179" s="29" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="27" t="n"/>
+      <c r="A180" s="44" t="n"/>
       <c r="B180" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23502,7 +23504,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="27" t="n"/>
+      <c r="A181" s="45" t="n"/>
       <c r="B181" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23562,7 +23564,7 @@
       <c r="H182" s="26" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="27" t="n"/>
+      <c r="A183" s="44" t="n"/>
       <c r="B183" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23592,7 +23594,7 @@
       <c r="H183" s="29" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="27" t="n"/>
+      <c r="A184" s="44" t="n"/>
       <c r="B184" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23622,7 +23624,7 @@
       <c r="H184" s="31" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="27" t="n"/>
+      <c r="A185" s="44" t="n"/>
       <c r="B185" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23652,7 +23654,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="27" t="n"/>
+      <c r="A186" s="44" t="n"/>
       <c r="B186" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23682,7 +23684,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="27" t="n"/>
+      <c r="A187" s="44" t="n"/>
       <c r="B187" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23712,7 +23714,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="27" t="n"/>
+      <c r="A188" s="45" t="n"/>
       <c r="B188" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23772,7 +23774,7 @@
       <c r="H189" s="36" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="27" t="n"/>
+      <c r="A190" s="44" t="n"/>
       <c r="B190" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23802,7 +23804,7 @@
       <c r="H190" s="31" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="27" t="n"/>
+      <c r="A191" s="44" t="n"/>
       <c r="B191" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23836,7 +23838,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="27" t="n"/>
+      <c r="A192" s="44" t="n"/>
       <c r="B192" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -23866,7 +23868,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="27" t="n"/>
+      <c r="A193" s="45" t="n"/>
       <c r="B193" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -23926,7 +23928,7 @@
       <c r="H194" s="26" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="27" t="n"/>
+      <c r="A195" s="44" t="n"/>
       <c r="B195" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23960,7 +23962,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="27" t="n"/>
+      <c r="A196" s="44" t="n"/>
       <c r="B196" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -23994,7 +23996,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="27" t="n"/>
+      <c r="A197" s="44" t="n"/>
       <c r="B197" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -24024,7 +24026,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="27" t="n"/>
+      <c r="A198" s="45" t="n"/>
       <c r="B198" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -24084,7 +24086,7 @@
       <c r="H199" s="36" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="27" t="n"/>
+      <c r="A200" s="44" t="n"/>
       <c r="B200" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24118,7 +24120,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="27" t="n"/>
+      <c r="A201" s="44" t="n"/>
       <c r="B201" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24148,7 +24150,7 @@
       <c r="H201" s="29" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="27" t="n"/>
+      <c r="A202" s="44" t="n"/>
       <c r="B202" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -24178,7 +24180,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="27" t="n"/>
+      <c r="A203" s="45" t="n"/>
       <c r="B203" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -24238,7 +24240,7 @@
       <c r="H204" s="26" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="27" t="n"/>
+      <c r="A205" s="44" t="n"/>
       <c r="B205" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24272,7 +24274,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="27" t="n"/>
+      <c r="A206" s="44" t="n"/>
       <c r="B206" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24306,7 +24308,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="27" t="n"/>
+      <c r="A207" s="44" t="n"/>
       <c r="B207" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -24336,7 +24338,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="27" t="n"/>
+      <c r="A208" s="45" t="n"/>
       <c r="B208" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -24396,7 +24398,7 @@
       <c r="H209" s="36" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="27" t="n"/>
+      <c r="A210" s="44" t="n"/>
       <c r="B210" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24430,7 +24432,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="27" t="n"/>
+      <c r="A211" s="44" t="n"/>
       <c r="B211" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24460,7 +24462,7 @@
       <c r="H211" s="29" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="27" t="n"/>
+      <c r="A212" s="44" t="n"/>
       <c r="B212" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -24490,7 +24492,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="27" t="n"/>
+      <c r="A213" s="45" t="n"/>
       <c r="B213" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -24550,7 +24552,7 @@
       <c r="H214" s="26" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="27" t="n"/>
+      <c r="A215" s="44" t="n"/>
       <c r="B215" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24584,7 +24586,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="27" t="n"/>
+      <c r="A216" s="44" t="n"/>
       <c r="B216" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24618,7 +24620,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="27" t="n"/>
+      <c r="A217" s="44" t="n"/>
       <c r="B217" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -24648,7 +24650,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="27" t="n"/>
+      <c r="A218" s="45" t="n"/>
       <c r="B218" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -24708,7 +24710,7 @@
       <c r="H219" s="36" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="27" t="n"/>
+      <c r="A220" s="44" t="n"/>
       <c r="B220" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24742,7 +24744,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="27" t="n"/>
+      <c r="A221" s="44" t="n"/>
       <c r="B221" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24772,7 +24774,7 @@
       <c r="H221" s="29" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="27" t="n"/>
+      <c r="A222" s="44" t="n"/>
       <c r="B222" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -24802,7 +24804,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="27" t="n"/>
+      <c r="A223" s="45" t="n"/>
       <c r="B223" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -24862,7 +24864,7 @@
       <c r="H224" s="26" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="27" t="n"/>
+      <c r="A225" s="44" t="n"/>
       <c r="B225" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24892,7 +24894,7 @@
       <c r="H225" s="29" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="27" t="n"/>
+      <c r="A226" s="44" t="n"/>
       <c r="B226" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -24926,7 +24928,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="27" t="n"/>
+      <c r="A227" s="44" t="n"/>
       <c r="B227" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -24956,7 +24958,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="27" t="n"/>
+      <c r="A228" s="45" t="n"/>
       <c r="B228" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -25016,7 +25018,7 @@
       <c r="H229" s="36" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="27" t="n"/>
+      <c r="A230" s="44" t="n"/>
       <c r="B230" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25046,7 +25048,7 @@
       <c r="H230" s="31" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="27" t="n"/>
+      <c r="A231" s="44" t="n"/>
       <c r="B231" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25080,7 +25082,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="27" t="n"/>
+      <c r="A232" s="44" t="n"/>
       <c r="B232" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25110,7 +25112,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="27" t="n"/>
+      <c r="A233" s="45" t="n"/>
       <c r="B233" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -25170,7 +25172,7 @@
       <c r="H234" s="26" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="27" t="n"/>
+      <c r="A235" s="44" t="n"/>
       <c r="B235" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25200,7 +25202,7 @@
       <c r="H235" s="29" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="27" t="n"/>
+      <c r="A236" s="44" t="n"/>
       <c r="B236" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25234,7 +25236,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="27" t="n"/>
+      <c r="A237" s="44" t="n"/>
       <c r="B237" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25264,7 +25266,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="27" t="n"/>
+      <c r="A238" s="45" t="n"/>
       <c r="B238" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -25324,7 +25326,7 @@
       <c r="H239" s="36" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="27" t="n"/>
+      <c r="A240" s="44" t="n"/>
       <c r="B240" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25354,7 +25356,7 @@
       <c r="H240" s="31" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="27" t="n"/>
+      <c r="A241" s="44" t="n"/>
       <c r="B241" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25384,7 +25386,7 @@
       <c r="H241" s="29" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="27" t="n"/>
+      <c r="A242" s="44" t="n"/>
       <c r="B242" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25414,7 +25416,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="27" t="n"/>
+      <c r="A243" s="44" t="n"/>
       <c r="B243" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25444,7 +25446,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="27" t="n"/>
+      <c r="A244" s="45" t="n"/>
       <c r="B244" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -25504,7 +25506,7 @@
       <c r="H245" s="36" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="27" t="n"/>
+      <c r="A246" s="44" t="n"/>
       <c r="B246" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25534,7 +25536,7 @@
       <c r="H246" s="31" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="27" t="n"/>
+      <c r="A247" s="44" t="n"/>
       <c r="B247" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25568,7 +25570,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="27" t="n"/>
+      <c r="A248" s="44" t="n"/>
       <c r="B248" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25598,7 +25600,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="27" t="n"/>
+      <c r="A249" s="44" t="n"/>
       <c r="B249" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25628,7 +25630,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="27" t="n"/>
+      <c r="A250" s="45" t="n"/>
       <c r="B250" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -25688,7 +25690,7 @@
       <c r="H251" s="36" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="27" t="n"/>
+      <c r="A252" s="44" t="n"/>
       <c r="B252" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25718,7 +25720,7 @@
       <c r="H252" s="31" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="27" t="n"/>
+      <c r="A253" s="44" t="n"/>
       <c r="B253" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25748,7 +25750,7 @@
       <c r="H253" s="29" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="27" t="n"/>
+      <c r="A254" s="44" t="n"/>
       <c r="B254" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25778,7 +25780,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="27" t="n"/>
+      <c r="A255" s="45" t="n"/>
       <c r="B255" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -25838,7 +25840,7 @@
       <c r="H256" s="26" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="27" t="n"/>
+      <c r="A257" s="44" t="n"/>
       <c r="B257" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25868,7 +25870,7 @@
       <c r="H257" s="29" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="27" t="n"/>
+      <c r="A258" s="44" t="n"/>
       <c r="B258" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -25898,7 +25900,7 @@
       <c r="H258" s="31" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="27" t="n"/>
+      <c r="A259" s="44" t="n"/>
       <c r="B259" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25928,7 +25930,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="27" t="n"/>
+      <c r="A260" s="44" t="n"/>
       <c r="B260" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -25958,7 +25960,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="27" t="n"/>
+      <c r="A261" s="44" t="n"/>
       <c r="B261" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -25988,7 +25990,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="27" t="n"/>
+      <c r="A262" s="45" t="n"/>
       <c r="B262" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -26048,7 +26050,7 @@
       <c r="H263" s="36" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="27" t="n"/>
+      <c r="A264" s="44" t="n"/>
       <c r="B264" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26078,7 +26080,7 @@
       <c r="H264" s="31" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="27" t="n"/>
+      <c r="A265" s="44" t="n"/>
       <c r="B265" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26112,7 +26114,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="27" t="n"/>
+      <c r="A266" s="44" t="n"/>
       <c r="B266" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26142,7 +26144,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="27" t="n"/>
+      <c r="A267" s="45" t="n"/>
       <c r="B267" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -26202,7 +26204,7 @@
       <c r="H268" s="26" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="27" t="n"/>
+      <c r="A269" s="44" t="n"/>
       <c r="B269" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26232,7 +26234,7 @@
       <c r="H269" s="29" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="27" t="n"/>
+      <c r="A270" s="44" t="n"/>
       <c r="B270" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26262,7 +26264,7 @@
       <c r="H270" s="31" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="27" t="n"/>
+      <c r="A271" s="44" t="n"/>
       <c r="B271" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26292,7 +26294,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="27" t="n"/>
+      <c r="A272" s="44" t="n"/>
       <c r="B272" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26322,7 +26324,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="27" t="n"/>
+      <c r="A273" s="44" t="n"/>
       <c r="B273" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -26352,7 +26354,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="27" t="n"/>
+      <c r="A274" s="45" t="n"/>
       <c r="B274" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -26412,7 +26414,7 @@
       <c r="H275" s="36" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="27" t="n"/>
+      <c r="A276" s="44" t="n"/>
       <c r="B276" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26446,7 +26448,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="27" t="n"/>
+      <c r="A277" s="44" t="n"/>
       <c r="B277" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26476,7 +26478,7 @@
       <c r="H277" s="29" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="27" t="n"/>
+      <c r="A278" s="44" t="n"/>
       <c r="B278" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26506,7 +26508,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="27" t="n"/>
+      <c r="A279" s="45" t="n"/>
       <c r="B279" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -26566,7 +26568,7 @@
       <c r="H280" s="26" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="27" t="n"/>
+      <c r="A281" s="44" t="n"/>
       <c r="B281" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26596,7 +26598,7 @@
       <c r="H281" s="29" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="27" t="n"/>
+      <c r="A282" s="44" t="n"/>
       <c r="B282" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26626,7 +26628,7 @@
       <c r="H282" s="31" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="27" t="n"/>
+      <c r="A283" s="44" t="n"/>
       <c r="B283" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26656,7 +26658,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="27" t="n"/>
+      <c r="A284" s="45" t="n"/>
       <c r="B284" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -26716,7 +26718,7 @@
       <c r="H285" s="36" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="27" t="n"/>
+      <c r="A286" s="44" t="n"/>
       <c r="B286" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26746,7 +26748,7 @@
       <c r="H286" s="31" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="27" t="n"/>
+      <c r="A287" s="44" t="n"/>
       <c r="B287" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26776,7 +26778,7 @@
       <c r="H287" s="29" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="27" t="n"/>
+      <c r="A288" s="44" t="n"/>
       <c r="B288" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26806,7 +26808,7 @@
       <c r="H288" s="31" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="27" t="n"/>
+      <c r="A289" s="44" t="n"/>
       <c r="B289" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -26836,7 +26838,7 @@
       <c r="H289" s="29" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="27" t="n"/>
+      <c r="A290" s="44" t="n"/>
       <c r="B290" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26866,7 +26868,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="27" t="n"/>
+      <c r="A291" s="44" t="n"/>
       <c r="B291" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26896,7 +26898,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="27" t="n"/>
+      <c r="A292" s="44" t="n"/>
       <c r="B292" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26926,7 +26928,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="27" t="n"/>
+      <c r="A293" s="44" t="n"/>
       <c r="B293" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -26956,7 +26958,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="27" t="n"/>
+      <c r="A294" s="45" t="n"/>
       <c r="B294" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -27016,7 +27018,7 @@
       <c r="H295" s="36" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="27" t="n"/>
+      <c r="A296" s="44" t="n"/>
       <c r="B296" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -27046,7 +27048,7 @@
       <c r="H296" s="31" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="27" t="n"/>
+      <c r="A297" s="44" t="n"/>
       <c r="B297" s="28" t="inlineStr">
         <is>
           <t>1.5阶</t>
@@ -27076,7 +27078,7 @@
       <c r="H297" s="29" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="27" t="n"/>
+      <c r="A298" s="44" t="n"/>
       <c r="B298" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -27106,7 +27108,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="27" t="n"/>
+      <c r="A299" s="44" t="n"/>
       <c r="B299" s="33" t="inlineStr">
         <is>
           <t>2阶</t>
@@ -27136,7 +27138,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="27" t="n"/>
+      <c r="A300" s="44" t="n"/>
       <c r="B300" s="34" t="inlineStr">
         <is>
           <t>3阶</t>
@@ -27166,7 +27168,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="27" t="n"/>
+      <c r="A301" s="45" t="n"/>
       <c r="B301" s="34" t="inlineStr">
         <is>
           <t>3阶</t>

--- a/Output/万物有灵进化整理表.xlsx
+++ b/Output/万物有灵进化整理表.xlsx
@@ -768,7 +768,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>万物有灵进化整理表（源码 4.9）</t>
+          <t>万物有灵进化整理表（源码 4.13）</t>
         </is>
       </c>
     </row>
